--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36514.69</v>
+        <v>36943.03</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>53111.95</v>
+        <v>53610.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>65088.11</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>27894.91</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>25437.68</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8717.219999999999</v>
+        <v>8777.41</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>64756.16</v>
+        <v>65203.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10624.49</v>
+        <v>10697.85</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1582.94</v>
+        <v>1593.87</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>103347.8</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7637.95</v>
+        <v>7690.68</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>66151.25</v>
+        <v>66607.96000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11980.56</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22138.31</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27147.91</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1374.83</v>
+        <v>1379.08</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6929.5</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17934.88</v>
+        <v>17887.44</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1379.63</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8608.190000000001</v>
+        <v>8585.42</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22018.09</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>911.24</v>
+        <v>908.83</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1915.02</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>33208.45</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>22138.97</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1162.3</v>
+        <v>1146.81</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11069.49</v>
+        <v>10922.04</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2213.9</v>
+        <v>2170.56</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1372.62</v>
+        <v>1345.75</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1660.42</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>77265.00999999999</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1649.35</v>
+        <v>1624.92</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>31880.12</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>11955.05</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>77.48999999999999</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1660.42</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>221389.72</v>
+        <v>216839.78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ITRAVEL -  TRANSPORTE PRIVADO DE PASAJEROS</t>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2771-366-CM26</t>
+          <t>3710-375-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,32 +961,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10697.85</v>
+        <v>7690.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1485217-83-CM26</t>
+          <t>2771-366-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,32 +1022,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>INVERSIONES LOF SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>77.498.695-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1593.87</v>
+        <v>10697.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>1485217-83-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,32 +1083,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>104061.33</v>
+        <v>1593.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3710-375-CM26</t>
+          <t>2771-286-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,32 +1144,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7690.68</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057387-333-CM26</t>
+          <t>934-81-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,27 +1210,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>66607.96000000001</v>
+        <v>1548.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1392-57-CM26</t>
+          <t>1057387-333-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12017.6</v>
+        <v>66607.96000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,32 +1327,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22206.75</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27231.85</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2467-743-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1379.08</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>2467-743-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,27 +1515,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6911.17</v>
+        <v>1379.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2360-405-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,27 +1576,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17887.44</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>2360-405-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1375.98</v>
+        <v>17887.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4404-131-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,32 +1693,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8585.42</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1413021-18-CM26</t>
+          <t>4404-131-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.804.011-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>21959.86</v>
+        <v>8585.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2467-740-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>908.83</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>2467-740-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1909.96</v>
+        <v>908.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>1413021-18-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.804.011-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>33120.62</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4057-471-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.181.100-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>22080.42</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5522-57-CM26</t>
+          <t>4057-471-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1146.81</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1391-1204-CM26</t>
+          <t>5522-57-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.241.697-2</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10922.04</v>
+        <v>1146.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>1391-1204-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,37 +2176,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.241.697-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2170.56</v>
+        <v>10922.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>2416-170-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1345.75</v>
+        <v>2170.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>2416-171-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1627.92</v>
+        <v>1345.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4794-74-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TRANSPORTES SANTIAGO S A</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.621.600-1</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>75752.64</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5178-2776-CM26</t>
+          <t>4794-74-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TRANSPORTES SANTIAGO S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>78.621.600-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1624.92</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>5178-2776-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,37 +2481,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>31224.93</v>
+        <v>1624.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>11709.35</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>75.89</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1626.3</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,32 +2730,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,6 +2765,67 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
+        <v>1626.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1062807-63-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>62.000.590-8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>216839.78</v>
       </c>
     </row>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -867,7 +867,11 @@
           <t>77.171.057-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>77.549.439-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.498.695-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1245,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1493,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1802,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1795,7 +1819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>1413021-18-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1844,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>60.804.011-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,7 +1874,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1909.96</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="24">
@@ -1917,7 +1941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1413021-18-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,37 +1966,41 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.804.011-0</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>21959.86</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="26">
@@ -2222,7 +2250,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>4794-74-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,27 +2275,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSPORTES SANTIAGO S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>78.621.600-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2305,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2170.56</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,27 +2336,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2366,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1345.75</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>2416-170-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,27 +2397,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2427,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1627.92</v>
+        <v>2170.56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4794-74-CM26</t>
+          <t>2416-171-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,27 +2458,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRANSPORTES SANTIAGO S A</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.621.600-1</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,7 +2488,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>75752.64</v>
+        <v>1345.75</v>
       </c>
     </row>
     <row r="34">
@@ -2697,7 +2725,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2790,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2771,61 +2807,126 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>4215-18-SE26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.104.022-9</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>84491.62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>1062807-63-CM26</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>62.000.590-8</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Ñuble</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>David Isaac</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>76.820.816-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>216839.78</v>
       </c>
     </row>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -1432,7 +1432,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1991,7 +1995,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
